--- a/data/test_data_swing_mobile.xlsx
+++ b/data/test_data_swing_mobile.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16360" tabRatio="500" firstSheet="4" activeTab="10"/>
+    <workbookView windowHeight="17160" tabRatio="500" firstSheet="4" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="560">
   <si>
     <t>TC_ID</t>
   </si>
@@ -1619,6 +1619,9 @@
     <t>HOW_MUCH_SCHEDULE</t>
   </si>
   <si>
+    <t>ADDITIONAL_ITEMS</t>
+  </si>
+  <si>
     <t>TC_MLTS_001</t>
   </si>
   <si>
@@ -1677,6 +1680,48 @@
   </si>
   <si>
     <t>Verify user can book venue end to end until payment</t>
+  </si>
+  <si>
+    <t>TC_MLTS_009</t>
+  </si>
+  <si>
+    <t>Verify user can add additional things</t>
+  </si>
+  <si>
+    <t>SWING BILLIARD :)</t>
+  </si>
+  <si>
+    <t>table_1</t>
+  </si>
+  <si>
+    <t>BALLS</t>
+  </si>
+  <si>
+    <t>TC_MLTS_010</t>
+  </si>
+  <si>
+    <t>Verify user can add additional multiple things</t>
+  </si>
+  <si>
+    <t>BALLS,BAG</t>
+  </si>
+  <si>
+    <t>TC_MLTS_011</t>
+  </si>
+  <si>
+    <t>Verify user can remove additional things</t>
+  </si>
+  <si>
+    <t>TC_MLTS_012</t>
+  </si>
+  <si>
+    <t>Verify user can remove additional multiple things</t>
+  </si>
+  <si>
+    <t>TC_MLTS_013</t>
+  </si>
+  <si>
+    <t>Verify user can select only single schedule</t>
   </si>
 </sst>
 </file>
@@ -2093,12 +2138,57 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2213,7 +2303,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2225,34 +2315,34 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2337,12 +2427,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2834,28 +2933,28 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:8">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3054,130 +3153,130 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:9">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="6" t="s">
         <v>488</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="6" t="s">
         <v>489</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:9">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="7" t="s">
         <v>492</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4" t="s">
+      <c r="D2" s="7"/>
+      <c r="E2" s="7" t="s">
         <v>494</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4" t="s">
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:9">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="7" t="s">
         <v>497</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="7" t="s">
         <v>499</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="7"/>
+      <c r="G3" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4" t="s">
+      <c r="H3" s="7"/>
+      <c r="I3" s="7" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:9">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="7" t="s">
         <v>501</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="7" t="s">
         <v>502</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>503</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="7" t="s">
         <v>499</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4" t="s">
+      <c r="H4" s="7"/>
+      <c r="I4" s="7" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:9">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="8" t="s">
         <v>505</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="8" t="s">
         <v>506</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="8" t="s">
         <v>509</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="8" t="s">
         <v>510</v>
       </c>
       <c r="I5" t="s">
@@ -3185,28 +3284,28 @@
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:9">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="8" t="s">
         <v>512</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="8" t="s">
         <v>513</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="8" t="s">
         <v>510</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="8" t="s">
         <v>509</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="8" t="s">
         <v>508</v>
       </c>
       <c r="I6" t="s">
@@ -3214,49 +3313,49 @@
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:9">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="8" t="s">
         <v>515</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="8" t="s">
         <v>516</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="8" t="s">
         <v>509</v>
       </c>
-      <c r="G7" s="5"/>
+      <c r="G7" s="8"/>
       <c r="I7" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:9">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="8" t="s">
         <v>518</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="8" t="s">
         <v>509</v>
       </c>
-      <c r="G8" s="5"/>
+      <c r="G8" s="8"/>
       <c r="I8" t="s">
         <v>520</v>
       </c>
@@ -3271,20 +3370,20 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14.1428571428571" customWidth="1"/>
     <col min="2" max="2" width="47.7142857142857" customWidth="1"/>
     <col min="3" max="3" width="27.2232142857143" customWidth="1"/>
-    <col min="4" max="4" width="14.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="18.8928571428571" customWidth="1"/>
     <col min="5" max="5" width="18.0714285714286" customWidth="1"/>
     <col min="6" max="6" width="24.5714285714286" customWidth="1"/>
     <col min="7" max="7" width="15.5" customWidth="1"/>
-    <col min="8" max="8" width="20.0714285714286" customWidth="1"/>
+    <col min="8" max="9" width="20.0714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="29" spans="1:8">
+    <row r="1" ht="15" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3307,182 +3406,310 @@
         <v>382</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>527</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>531</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>530</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F5" s="2">
         <v>2</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>536</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>535</v>
       </c>
       <c r="F6" s="2">
         <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F7" s="2">
         <v>2</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F8" s="2">
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="H8" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F9" s="2">
         <v>2</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="H9" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2" t="s">
         <v>135</v>
       </c>
+    </row>
+    <row r="10" ht="15.75" spans="1:9">
+      <c r="A10" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D10" t="s">
+        <v>548</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D11" t="s">
+        <v>548</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" spans="1:9">
+      <c r="A12" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D12" t="s">
+        <v>548</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" spans="1:9">
+      <c r="A13" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D13" t="s">
+        <v>548</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="1:9">
+      <c r="A14" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3516,61 +3743,61 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:19">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="P1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="Q1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="R1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="S1" s="15" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3940,2627 +4167,2627 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:23">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="8" t="s">
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="11" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7" t="s">
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="8" t="s">
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="11" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:23">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7" t="s">
+      <c r="I4" s="10"/>
+      <c r="J4" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="10">
         <v>3</v>
       </c>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="8" t="s">
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="12"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="11" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7" t="s">
+      <c r="I5" s="10"/>
+      <c r="J5" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="10">
         <v>2</v>
       </c>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7" t="s">
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="8" t="s">
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="11" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7" t="s">
+      <c r="I6" s="10"/>
+      <c r="J6" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="10">
         <v>2</v>
       </c>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7" t="s">
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="8" t="s">
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="11" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="K7" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="10">
         <v>2</v>
       </c>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7" t="s">
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="8" t="s">
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="11" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7" t="s">
+      <c r="I8" s="10"/>
+      <c r="J8" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="K8" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="10">
         <v>2</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="M8" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7" t="s">
+      <c r="N8" s="10"/>
+      <c r="O8" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="8" t="s">
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="12"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="11" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="K9" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9" s="10">
         <v>2</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="M9" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7" t="s">
+      <c r="N9" s="10"/>
+      <c r="O9" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="8" t="s">
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="12"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="11" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="10" ht="33" customHeight="1" spans="1:23">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7" t="s">
+      <c r="I10" s="10"/>
+      <c r="J10" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="K10" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="L10" s="7">
+      <c r="L10" s="10">
         <v>2</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="M10" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="N10" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="O10" s="7" t="s">
+      <c r="O10" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="8" t="s">
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="12"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="11" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="11" ht="33" customHeight="1" spans="1:23">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="K11" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="10">
         <v>2</v>
       </c>
-      <c r="M11" s="7" t="s">
+      <c r="M11" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="N11" s="7" t="s">
+      <c r="N11" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="O11" s="7" t="s">
+      <c r="O11" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="8" t="s">
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="12"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="11" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7" t="s">
+      <c r="I12" s="10"/>
+      <c r="J12" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="K12" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="10">
         <v>2</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="M12" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7" t="s">
+      <c r="N12" s="10"/>
+      <c r="O12" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="8" t="s">
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="12"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="11" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="K13" s="7" t="s">
+      <c r="K13" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="L13" s="7">
+      <c r="L13" s="10">
         <v>2</v>
       </c>
-      <c r="M13" s="7" t="s">
+      <c r="M13" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7" t="s">
+      <c r="N13" s="10"/>
+      <c r="O13" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="8" t="s">
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="12"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="11" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7" t="s">
+      <c r="I14" s="10"/>
+      <c r="J14" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="K14" s="7" t="s">
+      <c r="K14" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="L14" s="7">
+      <c r="L14" s="10">
         <v>2</v>
       </c>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7" t="s">
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="9"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="8" t="s">
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="12"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="11" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="K15" s="7" t="s">
+      <c r="K15" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="L15" s="7">
+      <c r="L15" s="10">
         <v>2</v>
       </c>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7" t="s">
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="9"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="8" t="s">
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="11" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7" t="s">
+      <c r="I16" s="10"/>
+      <c r="J16" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="K16" s="7" t="s">
+      <c r="K16" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="L16" s="7">
+      <c r="L16" s="10">
         <v>2</v>
       </c>
-      <c r="M16" s="7" t="s">
+      <c r="M16" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7" t="s">
+      <c r="N16" s="10"/>
+      <c r="O16" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="9"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="8" t="s">
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="12"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="11" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="J17" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="K17" s="7" t="s">
+      <c r="K17" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="L17" s="7">
+      <c r="L17" s="10">
         <v>2</v>
       </c>
-      <c r="M17" s="7" t="s">
+      <c r="M17" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7" t="s">
+      <c r="N17" s="10"/>
+      <c r="O17" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="9"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="8" t="s">
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="12"/>
+      <c r="V17" s="10"/>
+      <c r="W17" s="11" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7" t="s">
+      <c r="I18" s="10"/>
+      <c r="J18" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="K18" s="7" t="s">
+      <c r="K18" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="L18" s="7">
+      <c r="L18" s="10">
         <v>2</v>
       </c>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7">
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10">
         <v>30</v>
       </c>
-      <c r="Q18" s="7" t="s">
+      <c r="Q18" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="R18" s="7" t="s">
+      <c r="R18" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="9"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="8" t="s">
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="12"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="11" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="H19" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="J19" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="K19" s="7" t="s">
+      <c r="K19" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="L19" s="7">
+      <c r="L19" s="10">
         <v>2</v>
       </c>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7">
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10">
         <v>30</v>
       </c>
-      <c r="Q19" s="7" t="s">
+      <c r="Q19" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="R19" s="7" t="s">
+      <c r="R19" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="9"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="8" t="s">
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="12"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="11" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7" t="s">
+      <c r="I20" s="10"/>
+      <c r="J20" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="K20" s="7" t="s">
+      <c r="K20" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="L20" s="7">
+      <c r="L20" s="10">
         <v>2</v>
       </c>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7" t="s">
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="T20" s="7" t="s">
+      <c r="T20" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="U20" s="9" t="s">
+      <c r="U20" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="V20" s="7" t="s">
+      <c r="V20" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="W20" s="8" t="s">
+      <c r="W20" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I21" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="J21" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="K21" s="7" t="s">
+      <c r="K21" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="L21" s="7">
+      <c r="L21" s="10">
         <v>2</v>
       </c>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7" t="s">
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="T21" s="7" t="s">
+      <c r="T21" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="U21" s="9" t="s">
+      <c r="U21" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="V21" s="7" t="s">
+      <c r="V21" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="W21" s="8" t="s">
+      <c r="W21" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="9"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="8" t="s">
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="10"/>
+      <c r="U22" s="12"/>
+      <c r="V22" s="10"/>
+      <c r="W22" s="11" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="23" ht="33" customHeight="1" spans="1:23">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7" t="s">
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
-      <c r="U23" s="9"/>
-      <c r="V23" s="7"/>
-      <c r="W23" s="8" t="s">
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="10"/>
+      <c r="U23" s="12"/>
+      <c r="V23" s="10"/>
+      <c r="W23" s="11" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="H24" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7" t="s">
+      <c r="I24" s="10"/>
+      <c r="J24" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="K24" s="7" t="s">
+      <c r="K24" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="L24" s="7">
+      <c r="L24" s="10">
         <v>3</v>
       </c>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="7"/>
-      <c r="T24" s="7"/>
-      <c r="U24" s="9"/>
-      <c r="V24" s="7"/>
-      <c r="W24" s="8" t="s">
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="10"/>
+      <c r="T24" s="10"/>
+      <c r="U24" s="12"/>
+      <c r="V24" s="10"/>
+      <c r="W24" s="11" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="H25" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7" t="s">
+      <c r="I25" s="10"/>
+      <c r="J25" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="K25" s="7" t="s">
+      <c r="K25" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="L25" s="7">
+      <c r="L25" s="10">
         <v>2</v>
       </c>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7" t="s">
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
-      <c r="R25" s="7"/>
-      <c r="S25" s="7"/>
-      <c r="T25" s="7"/>
-      <c r="U25" s="9"/>
-      <c r="V25" s="7"/>
-      <c r="W25" s="8" t="s">
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="10"/>
+      <c r="T25" s="10"/>
+      <c r="U25" s="12"/>
+      <c r="V25" s="10"/>
+      <c r="W25" s="11" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H26" s="7" t="s">
+      <c r="H26" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7" t="s">
+      <c r="I26" s="10"/>
+      <c r="J26" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="K26" s="7" t="s">
+      <c r="K26" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="L26" s="7">
+      <c r="L26" s="10">
         <v>2</v>
       </c>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7" t="s">
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="7"/>
-      <c r="R26" s="7"/>
-      <c r="S26" s="7"/>
-      <c r="T26" s="7"/>
-      <c r="U26" s="9"/>
-      <c r="V26" s="7"/>
-      <c r="W26" s="8" t="s">
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="10"/>
+      <c r="U26" s="12"/>
+      <c r="V26" s="10"/>
+      <c r="W26" s="11" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="G27" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="H27" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="I27" s="7" t="s">
+      <c r="I27" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J27" s="7" t="s">
+      <c r="J27" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="K27" s="7" t="s">
+      <c r="K27" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="L27" s="7">
+      <c r="L27" s="10">
         <v>2</v>
       </c>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7" t="s">
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="7"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="7"/>
-      <c r="T27" s="7"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="7"/>
-      <c r="W27" s="8" t="s">
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="10"/>
+      <c r="T27" s="10"/>
+      <c r="U27" s="12"/>
+      <c r="V27" s="10"/>
+      <c r="W27" s="11" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="H28" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7" t="s">
+      <c r="I28" s="10"/>
+      <c r="J28" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="K28" s="7" t="s">
+      <c r="K28" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="L28" s="7">
+      <c r="L28" s="10">
         <v>2</v>
       </c>
-      <c r="M28" s="7" t="s">
+      <c r="M28" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7" t="s">
+      <c r="N28" s="10"/>
+      <c r="O28" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="7"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="7"/>
-      <c r="T28" s="7"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="7"/>
-      <c r="W28" s="8" t="s">
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10"/>
+      <c r="T28" s="10"/>
+      <c r="U28" s="12"/>
+      <c r="V28" s="10"/>
+      <c r="W28" s="11" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="G29" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="H29" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="I29" s="7" t="s">
+      <c r="I29" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J29" s="7" t="s">
+      <c r="J29" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="K29" s="7" t="s">
+      <c r="K29" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="L29" s="7">
+      <c r="L29" s="10">
         <v>2</v>
       </c>
-      <c r="M29" s="7" t="s">
+      <c r="M29" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7" t="s">
+      <c r="N29" s="10"/>
+      <c r="O29" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="P29" s="7"/>
-      <c r="Q29" s="7"/>
-      <c r="R29" s="7"/>
-      <c r="S29" s="7"/>
-      <c r="T29" s="7"/>
-      <c r="U29" s="9"/>
-      <c r="V29" s="7"/>
-      <c r="W29" s="8" t="s">
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10"/>
+      <c r="T29" s="10"/>
+      <c r="U29" s="12"/>
+      <c r="V29" s="10"/>
+      <c r="W29" s="11" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="30" ht="33" customHeight="1" spans="1:23">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G30" s="7" t="s">
+      <c r="G30" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="H30" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7" t="s">
+      <c r="I30" s="10"/>
+      <c r="J30" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="K30" s="7" t="s">
+      <c r="K30" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="L30" s="7">
+      <c r="L30" s="10">
         <v>2</v>
       </c>
-      <c r="M30" s="7" t="s">
+      <c r="M30" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="N30" s="7" t="s">
+      <c r="N30" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="O30" s="7" t="s">
+      <c r="O30" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="7"/>
-      <c r="R30" s="7"/>
-      <c r="S30" s="7"/>
-      <c r="T30" s="7"/>
-      <c r="U30" s="9"/>
-      <c r="V30" s="7"/>
-      <c r="W30" s="8" t="s">
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10"/>
+      <c r="S30" s="10"/>
+      <c r="T30" s="10"/>
+      <c r="U30" s="12"/>
+      <c r="V30" s="10"/>
+      <c r="W30" s="11" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="31" ht="33" customHeight="1" spans="1:23">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="H31" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="I31" s="7" t="s">
+      <c r="I31" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J31" s="7" t="s">
+      <c r="J31" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="K31" s="7" t="s">
+      <c r="K31" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="L31" s="7">
+      <c r="L31" s="10">
         <v>2</v>
       </c>
-      <c r="M31" s="7" t="s">
+      <c r="M31" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="N31" s="7" t="s">
+      <c r="N31" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="O31" s="7" t="s">
+      <c r="O31" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="P31" s="7"/>
-      <c r="Q31" s="7"/>
-      <c r="R31" s="7"/>
-      <c r="S31" s="7"/>
-      <c r="T31" s="7"/>
-      <c r="U31" s="9"/>
-      <c r="V31" s="7"/>
-      <c r="W31" s="8" t="s">
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
+      <c r="S31" s="10"/>
+      <c r="T31" s="10"/>
+      <c r="U31" s="12"/>
+      <c r="V31" s="10"/>
+      <c r="W31" s="11" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="32" ht="33" customHeight="1" spans="1:23">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="H32" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7" t="s">
+      <c r="I32" s="10"/>
+      <c r="J32" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="K32" s="7" t="s">
+      <c r="K32" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="L32" s="7">
+      <c r="L32" s="10">
         <v>2</v>
       </c>
-      <c r="M32" s="7" t="s">
+      <c r="M32" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7" t="s">
+      <c r="N32" s="10"/>
+      <c r="O32" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="7"/>
-      <c r="R32" s="7"/>
-      <c r="S32" s="7"/>
-      <c r="T32" s="7"/>
-      <c r="U32" s="9"/>
-      <c r="V32" s="7"/>
-      <c r="W32" s="8" t="s">
+      <c r="P32" s="10"/>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="10"/>
+      <c r="S32" s="10"/>
+      <c r="T32" s="10"/>
+      <c r="U32" s="12"/>
+      <c r="V32" s="10"/>
+      <c r="W32" s="11" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="33" ht="33" customHeight="1" spans="1:23">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G33" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H33" s="7" t="s">
+      <c r="H33" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="I33" s="7" t="s">
+      <c r="I33" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J33" s="7" t="s">
+      <c r="J33" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="K33" s="7" t="s">
+      <c r="K33" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="L33" s="7">
+      <c r="L33" s="10">
         <v>2</v>
       </c>
-      <c r="M33" s="7" t="s">
+      <c r="M33" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7" t="s">
+      <c r="N33" s="10"/>
+      <c r="O33" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="7"/>
-      <c r="R33" s="7"/>
-      <c r="S33" s="7"/>
-      <c r="T33" s="7"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="7"/>
-      <c r="W33" s="8" t="s">
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
+      <c r="S33" s="10"/>
+      <c r="T33" s="10"/>
+      <c r="U33" s="12"/>
+      <c r="V33" s="10"/>
+      <c r="W33" s="11" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G34" s="7" t="s">
+      <c r="G34" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H34" s="7" t="s">
+      <c r="H34" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7" t="s">
+      <c r="I34" s="10"/>
+      <c r="J34" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="K34" s="7" t="s">
+      <c r="K34" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="L34" s="7">
+      <c r="L34" s="10">
         <v>2</v>
       </c>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-      <c r="O34" s="7" t="s">
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="7"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="7"/>
-      <c r="T34" s="7"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="7"/>
-      <c r="W34" s="8" t="s">
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
+      <c r="S34" s="10"/>
+      <c r="T34" s="10"/>
+      <c r="U34" s="12"/>
+      <c r="V34" s="10"/>
+      <c r="W34" s="11" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G35" s="7" t="s">
+      <c r="G35" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H35" s="7" t="s">
+      <c r="H35" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="I35" s="7" t="s">
+      <c r="I35" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J35" s="7" t="s">
+      <c r="J35" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="K35" s="7" t="s">
+      <c r="K35" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="L35" s="7">
+      <c r="L35" s="10">
         <v>2</v>
       </c>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="7" t="s">
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="P35" s="7"/>
-      <c r="Q35" s="7"/>
-      <c r="R35" s="7"/>
-      <c r="S35" s="7"/>
-      <c r="T35" s="7"/>
-      <c r="U35" s="9"/>
-      <c r="V35" s="7"/>
-      <c r="W35" s="8" t="s">
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
+      <c r="U35" s="12"/>
+      <c r="V35" s="10"/>
+      <c r="W35" s="11" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="36" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G36" s="7" t="s">
+      <c r="G36" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="H36" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7" t="s">
+      <c r="I36" s="10"/>
+      <c r="J36" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="K36" s="7" t="s">
+      <c r="K36" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="L36" s="7">
+      <c r="L36" s="10">
         <v>2</v>
       </c>
-      <c r="M36" s="7" t="s">
+      <c r="M36" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="N36" s="7"/>
-      <c r="O36" s="7" t="s">
+      <c r="N36" s="10"/>
+      <c r="O36" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="7"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="7"/>
-      <c r="T36" s="7"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="7"/>
-      <c r="W36" s="8" t="s">
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="10"/>
+      <c r="T36" s="10"/>
+      <c r="U36" s="12"/>
+      <c r="V36" s="10"/>
+      <c r="W36" s="11" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G37" s="7" t="s">
+      <c r="G37" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H37" s="7" t="s">
+      <c r="H37" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="I37" s="7" t="s">
+      <c r="I37" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J37" s="7" t="s">
+      <c r="J37" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="K37" s="7" t="s">
+      <c r="K37" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="L37" s="7">
+      <c r="L37" s="10">
         <v>2</v>
       </c>
-      <c r="M37" s="7" t="s">
+      <c r="M37" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="N37" s="7"/>
-      <c r="O37" s="7" t="s">
+      <c r="N37" s="10"/>
+      <c r="O37" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="P37" s="7"/>
-      <c r="Q37" s="7"/>
-      <c r="R37" s="7"/>
-      <c r="S37" s="7"/>
-      <c r="T37" s="7"/>
-      <c r="U37" s="9"/>
-      <c r="V37" s="7"/>
-      <c r="W37" s="8" t="s">
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
+      <c r="U37" s="12"/>
+      <c r="V37" s="10"/>
+      <c r="W37" s="11" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="38" ht="33" customHeight="1" spans="1:23">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G38" s="7" t="s">
+      <c r="G38" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="H38" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7" t="s">
+      <c r="I38" s="10"/>
+      <c r="J38" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="K38" s="7" t="s">
+      <c r="K38" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="L38" s="7">
+      <c r="L38" s="10">
         <v>2</v>
       </c>
-      <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
-      <c r="O38" s="7" t="s">
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="P38" s="7">
+      <c r="P38" s="10">
         <v>9</v>
       </c>
-      <c r="Q38" s="7" t="s">
+      <c r="Q38" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="R38" s="7" t="s">
+      <c r="R38" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="S38" s="7"/>
-      <c r="T38" s="7"/>
-      <c r="U38" s="9"/>
-      <c r="V38" s="7"/>
-      <c r="W38" s="8" t="s">
+      <c r="S38" s="10"/>
+      <c r="T38" s="10"/>
+      <c r="U38" s="12"/>
+      <c r="V38" s="10"/>
+      <c r="W38" s="11" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="39" ht="33" customHeight="1" spans="1:23">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G39" s="7" t="s">
+      <c r="G39" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H39" s="7" t="s">
+      <c r="H39" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="I39" s="7" t="s">
+      <c r="I39" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J39" s="7" t="s">
+      <c r="J39" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="K39" s="7" t="s">
+      <c r="K39" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="L39" s="7">
+      <c r="L39" s="10">
         <v>2</v>
       </c>
-      <c r="M39" s="7"/>
-      <c r="N39" s="7"/>
-      <c r="O39" s="7" t="s">
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="P39" s="7">
+      <c r="P39" s="10">
         <v>9</v>
       </c>
-      <c r="Q39" s="7" t="s">
+      <c r="Q39" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="R39" s="7" t="s">
+      <c r="R39" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="S39" s="7"/>
-      <c r="T39" s="7"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="7"/>
-      <c r="W39" s="8" t="s">
+      <c r="S39" s="10"/>
+      <c r="T39" s="10"/>
+      <c r="U39" s="12"/>
+      <c r="V39" s="10"/>
+      <c r="W39" s="11" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="40" ht="33" customHeight="1" spans="1:23">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G40" s="7" t="s">
+      <c r="G40" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H40" s="7" t="s">
+      <c r="H40" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7" t="s">
+      <c r="I40" s="10"/>
+      <c r="J40" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="K40" s="7" t="s">
+      <c r="K40" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="L40" s="7">
+      <c r="L40" s="10">
         <v>2</v>
       </c>
-      <c r="M40" s="7" t="s">
+      <c r="M40" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="N40" s="7"/>
-      <c r="O40" s="7" t="s">
+      <c r="N40" s="10"/>
+      <c r="O40" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="P40" s="7"/>
-      <c r="Q40" s="7"/>
-      <c r="R40" s="7"/>
-      <c r="S40" s="7" t="s">
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10"/>
+      <c r="S40" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="T40" s="7" t="s">
+      <c r="T40" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="U40" s="9" t="s">
+      <c r="U40" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="V40" s="7" t="s">
+      <c r="V40" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="W40" s="8" t="s">
+      <c r="W40" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="41" ht="33" customHeight="1" spans="1:23">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F41" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G41" s="7" t="s">
+      <c r="G41" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H41" s="7" t="s">
+      <c r="H41" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="I41" s="7" t="s">
+      <c r="I41" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J41" s="7" t="s">
+      <c r="J41" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="K41" s="7" t="s">
+      <c r="K41" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="L41" s="7">
+      <c r="L41" s="10">
         <v>2</v>
       </c>
-      <c r="M41" s="7" t="s">
+      <c r="M41" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="N41" s="7"/>
-      <c r="O41" s="7" t="s">
+      <c r="N41" s="10"/>
+      <c r="O41" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="P41" s="7"/>
-      <c r="Q41" s="7"/>
-      <c r="R41" s="7"/>
-      <c r="S41" s="7" t="s">
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="T41" s="7" t="s">
+      <c r="T41" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="U41" s="9" t="s">
+      <c r="U41" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="V41" s="7" t="s">
+      <c r="V41" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="W41" s="8" t="s">
+      <c r="W41" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G42" s="7" t="s">
+      <c r="G42" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="H42" s="7" t="s">
+      <c r="H42" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="I42" s="7" t="s">
+      <c r="I42" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J42" s="7" t="s">
+      <c r="J42" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="K42" s="7" t="s">
+      <c r="K42" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="L42" s="7">
+      <c r="L42" s="10">
         <v>2</v>
       </c>
-      <c r="M42" s="7"/>
-      <c r="N42" s="7"/>
-      <c r="O42" s="7" t="s">
+      <c r="M42" s="10"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="7"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="7"/>
-      <c r="T42" s="7"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="7"/>
-      <c r="W42" s="8" t="s">
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="10"/>
+      <c r="S42" s="10"/>
+      <c r="T42" s="10"/>
+      <c r="U42" s="12"/>
+      <c r="V42" s="10"/>
+      <c r="W42" s="11" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1" spans="1:23">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="F43" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G43" s="7" t="s">
+      <c r="G43" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="H43" s="7" t="s">
+      <c r="H43" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="I43" s="7" t="s">
+      <c r="I43" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J43" s="7" t="s">
+      <c r="J43" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="K43" s="7" t="s">
+      <c r="K43" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="L43" s="7">
+      <c r="L43" s="10">
         <v>2</v>
       </c>
-      <c r="M43" s="7" t="s">
+      <c r="M43" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="N43" s="7"/>
-      <c r="O43" s="7" t="s">
+      <c r="N43" s="10"/>
+      <c r="O43" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="P43" s="7"/>
-      <c r="Q43" s="7"/>
-      <c r="R43" s="7"/>
-      <c r="S43" s="7"/>
-      <c r="T43" s="7"/>
-      <c r="U43" s="9"/>
-      <c r="V43" s="7"/>
-      <c r="W43" s="8" t="s">
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
+      <c r="S43" s="10"/>
+      <c r="T43" s="10"/>
+      <c r="U43" s="12"/>
+      <c r="V43" s="10"/>
+      <c r="W43" s="11" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="44" ht="33" customHeight="1" spans="1:23">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="F44" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G44" s="7" t="s">
+      <c r="G44" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="H44" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="I44" s="7" t="s">
+      <c r="I44" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J44" s="7" t="s">
+      <c r="J44" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="K44" s="7" t="s">
+      <c r="K44" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="L44" s="7">
+      <c r="L44" s="10">
         <v>2</v>
       </c>
-      <c r="M44" s="7" t="s">
+      <c r="M44" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="N44" s="7" t="s">
+      <c r="N44" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="O44" s="7" t="s">
+      <c r="O44" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="P44" s="7"/>
-      <c r="Q44" s="7"/>
-      <c r="R44" s="7"/>
-      <c r="S44" s="7"/>
-      <c r="T44" s="7"/>
-      <c r="U44" s="9"/>
-      <c r="V44" s="7"/>
-      <c r="W44" s="8" t="s">
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
+      <c r="S44" s="10"/>
+      <c r="T44" s="10"/>
+      <c r="U44" s="12"/>
+      <c r="V44" s="10"/>
+      <c r="W44" s="11" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="45" ht="33" customHeight="1" spans="1:23">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E45" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="F45" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G45" s="7" t="s">
+      <c r="G45" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="H45" s="7" t="s">
+      <c r="H45" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="I45" s="7" t="s">
+      <c r="I45" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J45" s="7" t="s">
+      <c r="J45" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="K45" s="7" t="s">
+      <c r="K45" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="L45" s="7">
+      <c r="L45" s="10">
         <v>2</v>
       </c>
-      <c r="M45" s="7"/>
-      <c r="N45" s="7"/>
-      <c r="O45" s="7" t="s">
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="P45" s="7"/>
-      <c r="Q45" s="7"/>
-      <c r="R45" s="7"/>
-      <c r="S45" s="7"/>
-      <c r="T45" s="7"/>
-      <c r="U45" s="9"/>
-      <c r="V45" s="7"/>
-      <c r="W45" s="8" t="s">
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="10"/>
+      <c r="T45" s="10"/>
+      <c r="U45" s="12"/>
+      <c r="V45" s="10"/>
+      <c r="W45" s="11" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="46" ht="33" customHeight="1" spans="1:23">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="F46" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G46" s="7" t="s">
+      <c r="G46" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="H46" s="7" t="s">
+      <c r="H46" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="I46" s="7" t="s">
+      <c r="I46" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J46" s="7" t="s">
+      <c r="J46" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="K46" s="7" t="s">
+      <c r="K46" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="L46" s="7">
+      <c r="L46" s="10">
         <v>2</v>
       </c>
-      <c r="M46" s="7"/>
-      <c r="N46" s="7"/>
-      <c r="O46" s="7" t="s">
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="P46" s="7"/>
-      <c r="Q46" s="7"/>
-      <c r="R46" s="7"/>
-      <c r="S46" s="7"/>
-      <c r="T46" s="7"/>
-      <c r="U46" s="9"/>
-      <c r="V46" s="7"/>
-      <c r="W46" s="8" t="s">
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
+      <c r="S46" s="10"/>
+      <c r="T46" s="10"/>
+      <c r="U46" s="12"/>
+      <c r="V46" s="10"/>
+      <c r="W46" s="11" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="47" ht="33" customHeight="1" spans="1:23">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="E47" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F47" s="7" t="s">
+      <c r="F47" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="7" t="s">
+      <c r="G47" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="H47" s="7" t="s">
+      <c r="H47" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="I47" s="7" t="s">
+      <c r="I47" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J47" s="7" t="s">
+      <c r="J47" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="K47" s="7" t="s">
+      <c r="K47" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="L47" s="7">
+      <c r="L47" s="10">
         <v>2</v>
       </c>
-      <c r="M47" s="7"/>
-      <c r="N47" s="7"/>
-      <c r="O47" s="7" t="s">
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="P47" s="7"/>
-      <c r="Q47" s="7"/>
-      <c r="R47" s="7"/>
-      <c r="S47" s="7"/>
-      <c r="T47" s="7"/>
-      <c r="U47" s="9"/>
-      <c r="V47" s="7"/>
-      <c r="W47" s="8" t="s">
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
+      <c r="S47" s="10"/>
+      <c r="T47" s="10"/>
+      <c r="U47" s="12"/>
+      <c r="V47" s="10"/>
+      <c r="W47" s="11" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="48" ht="33" customHeight="1" spans="1:23">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E48" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="F48" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G48" s="7" t="s">
+      <c r="G48" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H48" s="7" t="s">
+      <c r="H48" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="I48" s="7" t="s">
+      <c r="I48" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J48" s="7" t="s">
+      <c r="J48" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="K48" s="7" t="s">
+      <c r="K48" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="L48" s="7">
+      <c r="L48" s="10">
         <v>2</v>
       </c>
-      <c r="M48" s="7"/>
-      <c r="N48" s="7"/>
-      <c r="O48" s="7" t="s">
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="P48" s="7"/>
-      <c r="Q48" s="7"/>
-      <c r="R48" s="7"/>
-      <c r="S48" s="7"/>
-      <c r="T48" s="7"/>
-      <c r="U48" s="9"/>
-      <c r="V48" s="7"/>
-      <c r="W48" s="8" t="s">
+      <c r="P48" s="10"/>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="10"/>
+      <c r="S48" s="10"/>
+      <c r="T48" s="10"/>
+      <c r="U48" s="12"/>
+      <c r="V48" s="10"/>
+      <c r="W48" s="11" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="49" ht="33" customHeight="1" spans="1:23">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E49" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F49" s="7" t="s">
+      <c r="F49" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G49" s="7" t="s">
+      <c r="G49" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H49" s="7" t="s">
+      <c r="H49" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="I49" s="7" t="s">
+      <c r="I49" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J49" s="7" t="s">
+      <c r="J49" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="K49" s="7" t="s">
+      <c r="K49" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="L49" s="7">
+      <c r="L49" s="10">
         <v>2</v>
       </c>
-      <c r="M49" s="7"/>
-      <c r="N49" s="7"/>
-      <c r="O49" s="7" t="s">
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="P49" s="7"/>
-      <c r="Q49" s="7"/>
-      <c r="R49" s="7"/>
-      <c r="S49" s="7"/>
-      <c r="T49" s="7"/>
-      <c r="U49" s="9"/>
-      <c r="V49" s="7"/>
-      <c r="W49" s="8" t="s">
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
+      <c r="S49" s="10"/>
+      <c r="T49" s="10"/>
+      <c r="U49" s="12"/>
+      <c r="V49" s="10"/>
+      <c r="W49" s="11" t="s">
         <v>297</v>
       </c>
     </row>
@@ -6586,233 +6813,233 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:3">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:3">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:3">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:3">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:3">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:3">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:3">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:3">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:3">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="10">
         <v>1</v>
       </c>
     </row>
@@ -6834,7 +7061,7 @@
       <c r="B23" t="s">
         <v>300</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="10">
         <v>5</v>
       </c>
     </row>
@@ -6853,7 +7080,7 @@
       <c r="A25" t="s">
         <v>223</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="10" t="s">
         <v>302</v>
       </c>
       <c r="C25">
@@ -6867,7 +7094,7 @@
       <c r="B26" t="s">
         <v>300</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="10">
         <v>5</v>
       </c>
     </row>
@@ -6897,7 +7124,7 @@
       <c r="A29" t="s">
         <v>230</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="10" t="s">
         <v>302</v>
       </c>
       <c r="C29">
@@ -6922,7 +7149,7 @@
       <c r="B31" t="s">
         <v>300</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="10">
         <v>5</v>
       </c>
     </row>
@@ -6955,7 +7182,7 @@
       <c r="B34" t="s">
         <v>300</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="10">
         <v>5</v>
       </c>
     </row>
@@ -6974,7 +7201,7 @@
       <c r="A36" t="s">
         <v>241</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="10" t="s">
         <v>302</v>
       </c>
       <c r="C36">
@@ -6988,7 +7215,7 @@
       <c r="B37" t="s">
         <v>300</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="10">
         <v>5</v>
       </c>
     </row>
@@ -6996,7 +7223,7 @@
       <c r="A38" t="s">
         <v>247</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="10" t="s">
         <v>302</v>
       </c>
       <c r="C38">
@@ -7010,7 +7237,7 @@
       <c r="B39" t="s">
         <v>300</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="10">
         <v>5</v>
       </c>
     </row>
@@ -7029,7 +7256,7 @@
       <c r="A41" t="s">
         <v>253</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="10" t="s">
         <v>302</v>
       </c>
       <c r="C41">
@@ -7071,43 +7298,43 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:13">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="14" t="s">
         <v>41</v>
       </c>
     </row>
@@ -7949,31 +8176,31 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:9">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="14" t="s">
         <v>383</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="14" t="s">
         <v>384</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="14" t="s">
         <v>386</v>
       </c>
     </row>
@@ -8956,40 +9183,40 @@
       </c>
     </row>
     <row r="2" ht="13.5" customHeight="1" spans="1:4">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
     </row>
     <row r="3" ht="13.5" customHeight="1" spans="1:4">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="13" t="s">
         <v>409</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="13" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="4" ht="13.5" customHeight="1" spans="1:4">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="13" t="s">
         <v>411</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="13" t="s">
         <v>413</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="13" t="s">
         <v>414</v>
       </c>
     </row>
@@ -9031,820 +9258,820 @@
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:18">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="9" t="s">
         <v>415</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="9" t="s">
         <v>421</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="9" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A2" s="7">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="11" t="s">
         <v>425</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="8" t="s">
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="11" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A3" s="7">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="10" t="s">
         <v>427</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="11" t="s">
         <v>428</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="8" t="s">
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="11" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A4" s="7">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="11" t="s">
         <v>431</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="8" t="s">
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="11" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A5" s="7">
+      <c r="A5" s="10">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="10" t="s">
         <v>433</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="11" t="s">
         <v>434</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7" t="s">
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="8" t="s">
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="11" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:18">
-      <c r="A6" s="7">
+      <c r="A6" s="10">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="10" t="s">
         <v>436</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="11" t="s">
         <v>437</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7" t="s">
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7" t="b">
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R6" s="8" t="s">
+      <c r="R6" s="11" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A7" s="7">
+      <c r="A7" s="10">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="10" t="s">
         <v>440</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7" t="s">
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="10">
         <v>1</v>
       </c>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7" t="b">
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R7" s="8" t="s">
+      <c r="R7" s="11" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A8" s="7">
+      <c r="A8" s="10">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="11" t="s">
         <v>445</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7" t="s">
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10" t="s">
         <v>446</v>
       </c>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7" t="b">
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="R8" s="8" t="s">
+      <c r="R8" s="11" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:18">
-      <c r="A9" s="7">
+      <c r="A9" s="10">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="8" t="s">
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="11" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A10" s="7">
+      <c r="A10" s="10">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="8" t="s">
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="11" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:18">
-      <c r="A11" s="7">
+      <c r="A11" s="10">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="10" t="s">
         <v>455</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="11" t="s">
         <v>456</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="8" t="s">
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="11" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A12" s="7">
+      <c r="A12" s="10">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="11" t="s">
         <v>459</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="10" t="s">
         <v>461</v>
       </c>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7" t="s">
+      <c r="J12" s="10"/>
+      <c r="K12" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="10">
         <v>1</v>
       </c>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7" t="b">
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="R12" s="8" t="s">
+      <c r="R12" s="11" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A13" s="7">
+      <c r="A13" s="10">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="10" t="s">
         <v>463</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="10" t="s">
         <v>465</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7" t="s">
+      <c r="J13" s="10"/>
+      <c r="K13" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="L13" s="7">
+      <c r="L13" s="10">
         <v>1</v>
       </c>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7" t="b">
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="R13" s="8" t="s">
+      <c r="R13" s="11" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A14" s="7">
+      <c r="A14" s="10">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="10" t="s">
         <v>467</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="11" t="s">
         <v>468</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7" t="s">
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="8" t="s">
+      <c r="Q14" s="10"/>
+      <c r="R14" s="11" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A15" s="7">
+      <c r="A15" s="10">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="10" t="s">
         <v>470</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7" t="s">
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="8" t="s">
+      <c r="Q15" s="10"/>
+      <c r="R15" s="11" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:18">
-      <c r="A16" s="7">
+      <c r="A16" s="10">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="10" t="s">
         <v>473</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="10" t="s">
         <v>461</v>
       </c>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7" t="s">
+      <c r="J16" s="10"/>
+      <c r="K16" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="L16" s="7">
+      <c r="L16" s="10">
         <v>1</v>
       </c>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7" t="s">
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="Q16" s="7" t="b">
+      <c r="Q16" s="10" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R16" s="8" t="s">
+      <c r="R16" s="11" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:18">
-      <c r="A17" s="7">
+      <c r="A17" s="10">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="10" t="s">
         <v>476</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="11" t="s">
         <v>477</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="10" t="s">
         <v>465</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7" t="s">
+      <c r="J17" s="10"/>
+      <c r="K17" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="L17" s="7">
+      <c r="L17" s="10">
         <v>1</v>
       </c>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7" t="s">
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="Q17" s="7" t="b">
+      <c r="Q17" s="10" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R17" s="8" t="s">
+      <c r="R17" s="11" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A18" s="7">
+      <c r="A18" s="10">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="10" t="s">
         <v>478</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="11" t="s">
         <v>479</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7" t="s">
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="8" t="s">
+      <c r="Q18" s="10"/>
+      <c r="R18" s="11" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1" spans="1:18">
-      <c r="A19" s="7">
+      <c r="A19" s="10">
         <v>18</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="10" t="s">
         <v>481</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7" t="s">
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10" t="s">
         <v>446</v>
       </c>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7" t="b">
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="R19" s="8" t="s">
+      <c r="R19" s="11" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:18">
-      <c r="A20" s="7">
+      <c r="A20" s="10">
         <v>19</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="10" t="s">
         <v>484</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="11" t="s">
         <v>485</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="8" t="s">
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="11" t="s">
         <v>486</v>
       </c>
     </row>

--- a/data/test_data_swing_mobile.xlsx
+++ b/data/test_data_swing_mobile.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17160" tabRatio="500" firstSheet="4" activeTab="10"/>
+    <workbookView windowHeight="17160" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="562">
   <si>
     <t>TC_ID</t>
   </si>
@@ -1722,6 +1722,12 @@
   </si>
   <si>
     <t>Verify user can select only single schedule</t>
+  </si>
+  <si>
+    <t>TC_MLTS_014</t>
+  </si>
+  <si>
+    <t>Verify user can book venue end to end until payment with add ons</t>
   </si>
 </sst>
 </file>
@@ -3370,11 +3376,11 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14.1428571428571" customWidth="1"/>
-    <col min="2" max="2" width="47.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="56.6964285714286" customWidth="1"/>
     <col min="3" max="3" width="27.2232142857143" customWidth="1"/>
     <col min="4" max="4" width="18.8928571428571" customWidth="1"/>
     <col min="5" max="5" width="18.0714285714286" customWidth="1"/>
@@ -3710,6 +3716,33 @@
         <v>1</v>
       </c>
       <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D15" t="s">
+        <v>548</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" t="s">
+        <v>553</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>135</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
